--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MINNESOTA_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MINNESOTA_2017.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C79">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C217">
@@ -9031,7 +9031,7 @@
         <v>60</v>
       </c>
       <c r="D482">
-        <v>0.009303768026050551</v>
+        <v>0.009303768026050553</v>
       </c>
     </row>
     <row r="483">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C605">
@@ -17275,7 +17275,7 @@
         <v>59</v>
       </c>
       <c r="D940">
-        <v>0.009148705225616375</v>
+        <v>0.009148705225616376</v>
       </c>
     </row>
     <row r="941">
